--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I526"/>
+  <dimension ref="A1:I568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>금일착수</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -20106,7 +20106,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -20967,7 +20967,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>계획완료</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -21804,7 +21804,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -22078,7 +22078,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>계획완료</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -22872,7 +22872,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>계획완료</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>금일착수</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -23443,19 +23443,1825 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>2026-09-07,2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>row_1525_0</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>W26BD6592</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>[VD-D0405] No.2 LBO VD-D0405 바닥 Platform 연결 계단 설치 작업</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>No.4 VDU</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
           <t>WO업체배정</t>
         </is>
       </c>
-      <c r="H526" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="I526" t="inlineStr">
-        <is>
-          <t>2026-09-07,2026-09-11</t>
-        </is>
-      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>row_1526_1</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>W26BD6591</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>No.2 LBO 사용하지 않는 완강기 철거 작업(4Ea)</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>No.4 VDU</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>금일착수</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>row_1527_2</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>W26BD6576</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>[밸브수리][FEED FILTER] [DS-F3305C] DS-F3305 C,E Bank F/O By-Pass Sol’ Valve 수리 작업</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>row_1528_3</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>W26BD6510</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>[AR-F5103A] AR-F5103A Element 점검 및 교체작업</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>No.2 SRP</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>row_1529_4</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>W26BD6508</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>[VD-D1109] VD-D1109 ( Blow Down Flash Drum ) S/G Leak 수리</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>No.2 VDU</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>row_1530_5</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>W26BD6507</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>[UC-D2307] UC-D2307 Purge STM Line Pinhole 수리작업</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Unicracker</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>row_1531_6</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>W26BD6398</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>VD-P1104B ( HCVGO ) Strainer 청소 작업</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>No.2 VDU</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>row_1532_7</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>W26BD6249</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>[CD-C0801A] Compressor Lube Oil 주입시설의 Valve 파손으로 인한 수리 작업</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>CDW공정</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>YMAC 생산관리</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>row_1533_8</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>W26BD6248</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>HHT공정 일상 Steam Tracing/Trap 수리 작업(26년도 월간 Noti 09월)</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>HHT (HBO)</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>기유생산2</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>row_1534_9</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>W26BD6247</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>3LBO공정 일상 Steam Tracing/Trap 수리 작업(26년도 월간 Noti 09월)</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>CDW공정</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>YMAC 생산관리</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>row_1535_10</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>W26BD3816</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>[Y-P0321B] No.1 LBO Y-P0321B Governor Leak Steam 밸브 교체</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>No.1 CDW (HBO)</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>row_1536_11</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>W26BD3811</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>[VD-PI1023] VD-PI1023 ( V1101 O/H ) Steam Tracing Leak수리</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>No.2 VDU</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>row_1537_12</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>W26BD3810</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>7BL V1101 LT1106옆 Utility Steam Line Pinhole 수리</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>No.2 VDU</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>row_1538_13</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>W26BD3784</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>[HT-F1101A] HT-F1101A Filter 청소 및 교체 작업</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>HHT (HBO)</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>기유생산2</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>row_1539_14</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>W26BD3783</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>[HT-F1101B] HT-F1101B Filter 청소 및 교체 작업</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>HHT (HBO)</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>기유생산2</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>row_1540_15</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>W26BD3782</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>[HT-F1101C] HT-F1101C Filter 청소 및 교체 작업</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>HHT (HBO)</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>기유생산2</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>row_1541_16</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>W26BD3762</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>[HP-PSV8973] HP-PSV8973, Inlet Nozzle Steam Tracing 설치</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>No.1 H2 plant</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>row_1542_17</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>W26BD3696</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>[VD-E0106] No.1 LBO VD-E0106 Tube Side Out 배관 Support 보강 작업(사진첨부).</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>No.3 VDU</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>row_1543_18</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>W26BD3677</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>HP-C8601 안전난간, 발끝막이판설치 (2m )</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>No.1 H2 plant</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>row_1544_19</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>W26BD3553</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>[DS-C3501B] DS-C3501B 1st 2nd 3rd N2 Blind Open 및 복구작업</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>row_1545_20</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>W26BD3387</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>No.2 LBO 현장 창고주위 비품 정리 작업</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>No.2 CDW</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>금일착수</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>row_1546_21</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>W26BD3377</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>NaoCl 주입구  비트 Drain 막힘 해소 작업</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>HOU Cooling Tower</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>row_1547_22</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>W26BD2962</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>[Y-X9111-D03] Y-X9111-D03 개방청소 작업</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>HOU Cooling Tower</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>row_1548_23</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>W26BD2953</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>HOU생산3팀 현장 Sport Shim Plate 보강작업</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>#2 VRDS UTOS</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>row_1549_24</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>W26BD2877</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>[Y-X0911-T1] 유해위험물질 자장탱크 수직사다리 출입 통행을 위한 Cover 설치 작업</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>CDW공정</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>YMAC 생산관리</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>row_1550_25</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>W26BD2876</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>[Y-X0908-T1] 유해위험물질 자장탱크 수직사다리 출입 통행을 위한 Cover 설치 작업</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>CDW공정</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>YMAC 생산관리</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>작업 중</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>row_1551_26</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>W26BD2875</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>[Y-X0907-P2B] X0907-P2AB Calibration Pot Leak 로 인한 수리 작업</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>CDW공정</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>YMAC 생산관리</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>row_1552_27</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>W26BD2874</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>[Y-X0907-P2A] X0907-P2AB Calibration Pot Leak 로 인한 수리 작업</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>CDW공정</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>YMAC 생산관리</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>row_1553_28</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>W26BD2872</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>[Y-X0907-P2B] X0907-P2AB Dampener Leak 수리 작업</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>CDW공정</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>YMAC 생산관리</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>row_1554_29</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>W26BD2871</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>[Y-X0907-P2A] X0907-P2AB Dampener Leak 수리 작업</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>CDW공정</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>YMAC 생산관리</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>row_1555_30</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>W26BD2493</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>윤활유 배합 드럼첨가제 투입호스 제작작업</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>배합- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>row_1556_31</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>W26BD2412</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>No.2 LBO 9월간 Steam Tracing 및 Trap수리 작업</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>No.4 VDU</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>row_1557_32</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>W26BD2411</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>No.1 LBO 9월간 Steam Tracing 및 Trap수리 작업</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>No.4 VDU</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>row_1558_33</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>W26BD2406</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>No.1 LBO Y-X0353 (Hydrazine Tank) M/U 용 계단 고정 작업</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>No.3 VDU</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>row_1559_34</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>W26BD2231</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>45BL 정리정돈 작업 (Bundle)</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>장치1팀</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>장치1팀</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>row_1560_35</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>W26BD2229</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>SOx Scrubber to Neutral Pit Line Spool설치작업</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Unicracker</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>row_1561_36</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>W26BD2159</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>[TG-F7802B] F7802B Filter Element 교체작업</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>#7 SRP</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>row_1562_37</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>W26BD2158</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>[SW-P7403] P7403 Suc' Strainer 청소작업</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>#7 SRP</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>row_1563_38</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>W26BD2157</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>[SW-P7303A] P7303A Suc' Strainer 청소작업</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>#7 SRP</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>row_1564_39</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>W26BD2156</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>[SW-P7303B] P7303B Suc' Strainer 청소작업</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>#7 SRP</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>row_1565_40</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>W26BD2096</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>[Y-X0311] No.1 LBO C/T Basin 배관 덮개 교체 작업(사진첨부)</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>No.1 CDW (HBO)</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>row_1566_77</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>W26BA1181</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>윤활유 출하 캐느포지역 안전걸이대 수리작업</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>윤활유공통시설</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -23627,7 +23627,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="I530" t="inlineStr"/>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -23629,7 +23629,7 @@
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-17,2026-09-18</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -24104,7 +24104,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="I541" t="inlineStr"/>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -24061,7 +24061,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="I540" t="inlineStr"/>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -21902,11 +21902,7 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="I491" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
+      <c r="I491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -24366,7 +24366,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="I547" t="inlineStr"/>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -23756,7 +23756,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="I533" t="inlineStr"/>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -25234,7 +25234,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I567" t="inlineStr"/>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -24327,7 +24327,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="I546" t="inlineStr"/>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -11655,7 +11655,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-01,2026-09-15</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -23537,7 +23537,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="I528" t="inlineStr"/>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -24554,7 +24554,11 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="I551" t="inlineStr"/>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -20116,7 +20116,7 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>2026-09-08,2026-09-10</t>
+          <t>2026-09-08,2026-09-10,2026-09-15</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -8750,7 +8750,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -12830,7 +12830,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -24114,7 +24114,7 @@
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-11,2026-09-17</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -23629,7 +23629,7 @@
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>2026-09-17,2026-09-18</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -23629,7 +23629,7 @@
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-18,2026-09-21</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -24902,7 +24902,11 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="I559" t="inlineStr"/>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -20975,7 +20975,11 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="I470" t="inlineStr"/>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -20116,7 +20116,7 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>2026-09-08,2026-09-10,2026-09-15</t>
+          <t>2026-09-08,2026-09-10,2026-09-15,2026-09-16</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I568"/>
+  <dimension ref="A1:I583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -20967,7 +20967,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>계획완료</t>
+          <t>금일착수</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -23533,7 +23533,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -24108,7 +24108,7 @@
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>계획완료</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -24597,7 +24597,7 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -24835,7 +24835,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>No.2 LBO 9월간 Steam Tracing 및 Trap수리 작업</t>
+          <t>No.2 LBO Steam leak 수리작업</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -24898,7 +24898,7 @@
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>금일착수</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -25302,6 +25302,651 @@
         </is>
       </c>
       <c r="I568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>row_1567_0</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>W26BD8350</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>[TG-F7702B] F7702B Filter Element 교체작업</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>#7 SRP</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>row_1568_1</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>W26BD8349</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>[TG-F7701] F7701 Filter Element 교체작업</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>#7 SRP</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>계획완료</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>row_1569_2</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>W26BD8335</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>[Y-CT9101] Y-CT9101 Screen 청소 작업</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>HOU Cooling Tower</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>row_1570_3</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>W26BD8164</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>No.2 LBO CM Trap 전단 Drain Tubing OWS로 연장 적업</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>No.4 VDU</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>row_1571_4</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>W26BD8163</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>No.1 LBO CM Trap 전단 Drain Tubing 으로 연장 적업</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>No.3 VDU</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>row_1572_6</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>W26BD7837</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>HOU 정비동 내 노후 배관 교체작업</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>기계1 Unit</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>기계</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>row_1573_7</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>W26BD7782</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>7BL 9월 보온/ 비계/Steam Tracing수리</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>No.1 H2 plant</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>row_1574_8</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>W26BD7779</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>[LB-SC04] 윤활유 자동화출하시설 S/C 사다리 수리작업</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>제품저장-소포장</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>row_1575_9</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>W26BD7778</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>[LB-SC03] 윤활유 자동화출하시설 S/C 사다리 수리작업</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>제품저장-소포장</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>row_1576_10</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>W26BD7777</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>윤활유 출하장 케노피 Air Line Leak 수리작업</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>제품출하-LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>row_1577_11</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>W26BD7776</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>윤활유 충전 2층 라벨실 이동식계단 설치작업</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>충전- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="inlineStr">
+        <is>
+          <t>row_1578_12</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>W26BD7775</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>윤활유 충전 4L Line  계단 Handrail 설치작업</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>충전- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="inlineStr">
+        <is>
+          <t>row_1579_13</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>W26BD7772</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>윤활유 충전 2층 4L Line Robot 방호망 수리작업</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>충전- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="inlineStr">
+        <is>
+          <t>row_1580_14</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>W26BD7771</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>윤활유 충전 부재료 이송 Lift 진입방지봉 수리작업</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>충전- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="inlineStr">
+        <is>
+          <t>row_1581_15</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>W26BD7696</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>[HPS01003-6"-K01B-HC] No.1 LBO HPS To 구 VD-E0108 Header 밸브 후단 Blind 설치(도면 첨부)</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>No.3 VDU</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -25430,7 +25430,11 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="I571" t="inlineStr"/>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -20116,7 +20116,7 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>2026-09-08,2026-09-10,2026-09-15,2026-09-16</t>
+          <t>2026-09-08,2026-09-10,2026-09-15,2026-09-16,2026-09-17</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -22704,7 +22704,11 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="I509" t="inlineStr"/>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -22706,7 +22706,7 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-14,2026-09-18</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -22706,7 +22706,7 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>2026-09-14,2026-09-18</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I583"/>
+  <dimension ref="A1:I586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20967,7 +20967,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -24112,7 +24112,7 @@
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>계획완료</t>
+          <t>금일착수</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -24902,7 +24902,7 @@
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -25383,7 +25383,7 @@
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>계획완료</t>
+          <t>금일착수</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -25955,6 +25955,135 @@
         </is>
       </c>
       <c r="I583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="inlineStr">
+        <is>
+          <t>row_1582_0</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>W26BD8655</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>[HT-F1101C] HT-F1101C 내부 Filter 교체 작업</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>HHT (HBO)</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>기유생산2</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>row_1583_1</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>W26BD8607</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>[HT-F1101B] HT-F1101B 내부 Filter 교체 작업</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>HHT (HBO)</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>기유생산2</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>row_1584_2</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>W26BD8574</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>[P06102-3"-BB11-PP-IH-25] No.2 LBO CD-D0505 O/G To PSA OBL Line Steam Tracing 설치 작업</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>No.4 VDU</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -26040,7 +26040,11 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="I585" t="inlineStr"/>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -26040,11 +26040,7 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="I585" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
+      <c r="I585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -24122,7 +24122,7 @@
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>2026-09-11,2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -25997,7 +25997,11 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="I584" t="inlineStr"/>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -23592,7 +23592,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="I529" t="inlineStr"/>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I586"/>
+  <dimension ref="A1:I613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -12177,7 +12177,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -19535,7 +19535,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -20106,7 +20106,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -20967,7 +20967,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -22078,7 +22078,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>계획완료</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -22516,7 +22516,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>계획완료</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -22966,7 +22966,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -23056,7 +23056,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>계획완료</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -23584,7 +23584,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -23631,7 +23631,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -24472,7 +24472,7 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -24820,7 +24820,7 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -24906,7 +24906,7 @@
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -25039,7 +25039,7 @@
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -25344,7 +25344,7 @@
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -25387,7 +25387,7 @@
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -25430,7 +25430,7 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>계획완료</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -25907,7 +25907,7 @@
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -26096,6 +26096,1167 @@
         </is>
       </c>
       <c r="I586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>row_1585_0</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>W26BG3551</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>[DS-C3501A-STR1] DS-C3501A-STR1 外 2 청소작업 및 Blind 작업</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>row_1586_1</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>W26BG3550</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>[DS-C3501A-STR1] DS-C3501A-STR1 外 2 청소작업 및 Blind 작업</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>row_1587_2</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>W26BG3549</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>[DS-C3501A-STR1] DS-C3501A-STR1 外 2 청소작업 및 Blind 작업</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>row_1588_3</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>W26BG3535</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>[Y-P0352A] No.1 LBO Y-P0352A HPS Trap 전후단 및 By pass 밸브 교체(3Ea)</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>No.1 CDW (HBO)</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>row_1589_4</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>W26BG3291</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>[DS-C3501B-STR1] DS-C3501B-STR1 外 1 Blind 주입작업 및 청소작업</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>이력완료</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>row_1590_5</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>W26BG3290</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>[DS-C3501B-STR1] DS-C3501B-STR1 外 1 Blind 주입작업 및 청소작업</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>row_1591_6</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>W26BG3209</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>[BFW03012-1 1/2"-F01B-HC-ST] No.1 LBO Y-X0355 M/U용 BFW Line Pinhole수리</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>No.1 CDW (HBO)</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>row_1592_7</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>W26BG3190</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>No.1 LBO 풍향계 수리 작업</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>No.3 VDU</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>이력완료</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>row_1593_8</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>W26BG3083</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>[YE-PSV10632] ME1032-P1A/B PSV10631탈착및 PSV10632 부착작업</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>#2 VRDS UTOS</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>이력완료</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>row_1594_9</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>W26BG2959</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>[DS-C3501B] DS-C3501B 1st 2nd 3rd N2 Blind Open 작업</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>이력완료</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>row_1595_10</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>W26BG2958</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>[DS-C3501B] DS-C3501B 2nd Suc'&amp;Disch' 격리 Blind 주입 작업</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>row_1596_11</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>W26BG2888</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>10월 STM Tracing수리작업</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Unicracker</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>row_1597_12</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>W26BG2840</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>10월 월간 STM Tracing 수리작업</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>#2 VRDS UTOS</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>작업 중</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>row_1598_14</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>W26BG2753</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>조정실 옥상 풍향계 교체작업</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Unicracker</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>이력완료</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>row_1599_15</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>W26BG2750</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>[DS-C3501A-STR1] DS-C3501A-STR1 外 1 청소 위한 Blind 작업 및 Strainer 청소 작업</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>row_1600_16</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>W26BG2749</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>[DS-C3501A-STR1] DS-C3501A-STR1 外 1 청소 위한 Blind 작업 및 Strainer 청소 작업</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>작업 중</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>row_1601_18</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>W26BG2607</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>F4198A Filter Element 교체</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>#2 VRDS</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>이력완료</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>row_1602_19</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>W26BG2403</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>HHT공정 그레이팅 수선 작업</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>HHT (HBO)</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>기유생산2</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>row_1603_20</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>W26BD9561</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>윤활유 충전 로레터 기어 안전커버 설치작업</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>충전- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>row_1604_21</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>W26BD9560</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>윤활유 충전 충전기 드레인 배관 개조작업</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>충전- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>row_1605_22</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>W26BD9314</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>HP-C8102D Lubricator Lube Oil Reservoir M/U용 Tubing 손상 교체</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>No.1 H2 plant</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>row_1606_23</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>W26BD8964</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>7BL DMDS 수령  ( 3DRUM ) 작업</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>No.1 H2 plant</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>이력완료</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>row_1607_24</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>W26BD8873</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>[Y-D9701] Y-D9701 2층,3층 안전난간 설치작업(3Point)</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>HOU부대시설</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>row_1608_25</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>W26BD8772</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>[Y-P0652B] No.2 LBO Y-P0652B Check Vlave By-Pass Body Pinhoe 수리작업.</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>No.4 VDU</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>row_1609_36</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>W26BD7781</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>윤활유 배합 Tank지역 스팀배관 Drain Point 수리작업</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>배합- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>이력완료</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>row_1610_47</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>W26BD6589</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>현장 안전바 고착으로 인한 수리작업</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>#2 VRDS UTOS</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>row_1611_66</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>W26BD3454</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>윤활유 충전장 2층 부재료창고 계단 손잡이 수리작업</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>충전- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -20243,7 +20243,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -26181,7 +26181,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="I588" t="inlineStr"/>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -26183,7 +26183,7 @@
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-28,2026-09-29</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -26130,7 +26130,7 @@
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -26736,7 +26736,7 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -26220,7 +26220,7 @@
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -26357,7 +26357,11 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="I592" t="inlineStr"/>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -26359,7 +26359,7 @@
       </c>
       <c r="I592" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-25,2026-09-29</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I613"/>
+  <dimension ref="A1:I631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25606,7 +25606,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>계획완료</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -26611,7 +26611,7 @@
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -27213,7 +27213,7 @@
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -27265,6 +27265,780 @@
         </is>
       </c>
       <c r="I613" t="inlineStr"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>row_1612_0</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>W26BG5515</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>윤활유 배합반 건물 우수관 개선작업</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>배합- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>row_1613_1</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>W26BG5392</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>윤활유 배합 Pig Receiver(PLR181) 개조작업</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>배합- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>row_1614_2</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>W26BG5391</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>윤활유 충전장 작업 발판 고정작업</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>충전- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>row_1615_3</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>W26BG5233</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>[TG-F7802A] F7802A Filter Element 교체작업</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>#7 SRP</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>금일착수</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>row_1616_4</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>W26BG4788</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>[SW-F7302B] F7302B Filter Element 교체작업</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>#7 SRP</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>row_1617_5</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>W26BG4664</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>윤활유 배합 Bulk출하 연결호스 설치작업</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>배합- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>row_1618_6</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>W26BG4663</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>윤활유 배합 LB-PR205 (Pig Receiver) Vent 연결관 수리작업</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>배합- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>금일착수</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>row_1619_7</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>W26BG4662</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>윤활유 배합 STM Tracing Leak 수리작업</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>배합- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>row_1620_8</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>W26BG4614</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>HOU 생산2팀 협력사 휴게시설 컨테이너 철거 작업</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>row_1621_9</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>W26BG4451</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>[HP-F8701] CO2 공정 F-8701 ELEMENT 교체 작업</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>No.1 H2 plant</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>row_1622_10</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>W26BG4449</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>F5203 Element 교체 작업</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>No.2 SRP</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>계획완료</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>row_1623_11</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>W26BG4448</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>[AR-F5103A] Element 점검 및 교체작업</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>No.2 SRP</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>row_1624_12</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>W26BG4445</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Safety Washer 점검 및 수리작업</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>No.2 SRP</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>row_1625_13</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>W26BG4402</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>[Y-P0661B] No.2 LBO Y-P0661B Sealing WTR Strainer 청소 작업</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>No.4 VDU</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>row_1626_14</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>W26BG4218</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>P2204 Purge STM Trap B/V Flange Leak 수리작업</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Unicracker</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>row_1627_15</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>W26BG4152</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>7BL 10월 TM TRACING 수리 작업</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>No.1 H2 plant</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>row_1628_16</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>W26BG4078</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>[Y-X9111-P03A] Y-X9111-P03A 전.후단 배관 재질 변경으로 인한 교체 작업</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>HOU Cooling Tower</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>row_1629_17</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>W26BG4077</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Y-X9111-D03] Y-X9111-D03 개방청소 작업</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>HOU Cooling Tower</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -27737,7 +27737,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="I624" t="inlineStr"/>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -27739,7 +27739,7 @@
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-02,2026-10-06</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -27784,7 +27784,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="I625" t="inlineStr"/>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -27786,7 +27786,7 @@
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-07,2026-10-08</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -26619,7 +26619,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="I598" t="inlineStr"/>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -25614,7 +25614,11 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="I575" t="inlineStr"/>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -28054,7 +28054,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="I631" t="inlineStr"/>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -28011,7 +28011,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="I630" t="inlineStr"/>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -27702,7 +27702,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="I623" t="inlineStr"/>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -28017,7 +28017,7 @@
       </c>
       <c r="I630" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30,2026-10-01</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -20433,7 +20433,7 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-04,2026-10-07</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -23412,7 +23412,11 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="I525" t="inlineStr"/>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -26889,7 +26889,11 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="I604" t="inlineStr"/>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -26891,7 +26891,7 @@
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28,2026-10-05</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -26891,7 +26891,7 @@
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>2026-09-28,2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -12701,7 +12701,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -23690,7 +23690,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="I531" t="inlineStr"/>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -23692,7 +23692,7 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-07,2026-10-12</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -26416,7 +26416,11 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="I593" t="inlineStr"/>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I631"/>
+  <dimension ref="A1:I636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -23682,7 +23682,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -25833,7 +25833,7 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -26408,7 +26408,7 @@
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -27323,7 +27323,7 @@
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>계획완료</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
@@ -27366,7 +27366,7 @@
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -27538,7 +27538,7 @@
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
@@ -27581,7 +27581,7 @@
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -27624,7 +27624,7 @@
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -27757,7 +27757,7 @@
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>계획완료</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -28083,6 +28083,221 @@
           <t>2026-10-01</t>
         </is>
       </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>row_1630_0</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>W26BG7036</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>[VD-P1104B] VD-P1104B(HCVGO PUMP) STRAINER  청소 작업</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>No.2 VDU</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>row_1631_1</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>W26BG6716</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>VD-LV1127(E1116C BFW) BY-PASS V/V STEM 수리 작업</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>No.2 VDU</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>row_1632_2</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>W26BG6543</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>HOU생산2팀 공정내 풍향계 교체작업</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>row_1633_3</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>W26BG6071</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>T7701 Amine(HS-103) Loading 작업</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>#7 SRP</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>row_1634_4</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>W26BG5649</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>[MPS03009-12"-F01B-HC] No.1 LBO PV0881 후단 Line Boot Leg Steam Leak 수리</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>No.1 CDW (HBO)</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -28125,7 +28125,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="I632" t="inlineStr"/>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I636"/>
+  <dimension ref="A1:I648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23682,7 +23682,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>계획완료</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -25747,7 +25747,7 @@
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -25790,7 +25790,7 @@
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -27323,7 +27323,7 @@
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>계획완료</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
@@ -27667,7 +27667,7 @@
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -28207,7 +28207,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -28302,6 +28302,522 @@
         </is>
       </c>
       <c r="I636" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>row_1635_0</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>W26BG8998</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>[AR-F5103] AR-F5103 Element 교체작업</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>No.2 SRP</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>계획완료</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>row_1636_1</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>W26BG8991</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>[DS-P4110A] P4110A Pump Seal 수리를 위한 Blind 작업</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>#2 VRDS</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>row_1637_2</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>W26BG8886</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>[TG-F7802B] F7802B Filter Element 교체작업</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>#7 SRP</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>row_1638_3</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>W26BG8487</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>No.1 LBO 10월 Steam Tracing 및 Trap 수리 작업</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>No.3 VDU</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>작업 중</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>row_1639_4</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>W26BG8486</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>No.2 LBO 10월 Steam Tracing 및 Trap 수리 작업</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>No.2 CDW</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>row_1640_5</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>W26BG8244</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>[DS-F4198B] F4198B Filter Element 교체작업</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>#2 VRDS</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>row_1641_6</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>W26BG8243</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>[TG-F7702A] F7702A Filter Element 교체작업</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>#7 SRP</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>row_1642_7</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>W26BG8231</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>[SR-P6501AR] SR-P6501AR 수리위한 배관 분리작업</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>No.2 SRP</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>row_1643_8</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>W26BG8228</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>[U93122-B01A-3"-SW-ST] No.1 LBO 4B/L 위치 Service Water Line Leak 수리 작업</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>No.1 CDW (HBO)</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>row_1644_9</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>W26BG8196</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>3LBO공정 일상 Steam Tracing/Trap 수리 작업(26년도 월간 Noti 10월)</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>CDW공정</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>YMAC 생산관리</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>row_1645_10</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>W26BG8195</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>HHT공정 일상 Steam Tracing/Trap 수리 작업(26년도 월간 Noti 10월)</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>HHT (HBO)</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>기유생산2</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>row_1646_11</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>W26BG8092</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>STH-TT-050 STM Tracing Valve고착 수리작업</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Unicracker</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I648"/>
+  <dimension ref="A1:I649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -27323,7 +27323,7 @@
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
@@ -27624,7 +27624,7 @@
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -27894,7 +27894,7 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -28293,7 +28293,7 @@
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -28336,7 +28336,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>계획완료</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -28818,6 +28818,49 @@
         </is>
       </c>
       <c r="I648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>row_1647_0</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>W26BH1125</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>[VD-P1105A] VD-P1105A(BTM PUMP) SUC' STRAINER 청소 작업</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>No.2 VDU</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -28860,7 +28860,11 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="I649" t="inlineStr"/>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -27902,7 +27902,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="I627" t="inlineStr"/>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -11434,7 +11434,11 @@
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I649"/>
+  <dimension ref="A1:I656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>금일착수</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -28172,7 +28172,7 @@
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>금일착수</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -28860,19 +28860,320 @@
       </c>
       <c r="G649" t="inlineStr">
         <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>row_1648_0</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>W26BK4037</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>[AR-F5103A] AR-F5103A Element 점검 및 교체작업</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>No.2 SRP</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
           <t>WO업체배정</t>
         </is>
       </c>
-      <c r="H649" t="inlineStr">
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>row_1649_1</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>W26BK3804</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>HOU공장 7BL 운전중 HP-V8107-1 검사를 위한 비계 및 전처리 작업</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>No.1 H2 plant</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>검사팀</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>row_1650_2</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>W26BH1515</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>[VD-D0405] No.2 LBO VD-D0405 바닥 Grating과 단차 부위 계단 설치</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>No.4 VDU</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="I649" t="inlineStr">
+      <c r="I652" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>row_1651_3</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>W26BH1418</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>[Y-D1239] Y-D1239 Inlet Line의 격리용 Blind 설치 작업</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>HHT (HBO)</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>기유생산2</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
+      <c r="I653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>row_1652_4</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>W26BH1381</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>11월 월간 STM Tracing 수리작업</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>#2 VRDS UTOS</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>row_1653_5</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>W26BH1227</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>윤활유 배합 STM Tracing 수리작업</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>배합- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>row_1654_6</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>W26BH1171</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>윤활유 충전 Strainer 제작작업</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>충전- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -28915,7 +28915,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="I650" t="inlineStr"/>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -28917,7 +28917,7 @@
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-22,2026-10-23</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -2431,7 +2431,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>MC(작업완료)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -28180,7 +28180,11 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="I633" t="inlineStr"/>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -27996,7 +27996,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="I629" t="inlineStr"/>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -27034,7 +27034,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="I607" t="inlineStr"/>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I656"/>
+  <dimension ref="A1:I674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -20067,7 +20067,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -21902,7 +21902,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -23365,7 +23365,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>금일착수</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -24218,7 +24218,7 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>계획완료</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -24527,7 +24527,7 @@
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -25618,7 +25618,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -26631,7 +26631,7 @@
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -26678,7 +26678,7 @@
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -26807,7 +26807,7 @@
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -27859,7 +27859,7 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -27992,7 +27992,7 @@
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -28180,7 +28180,7 @@
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>금일착수</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -28485,7 +28485,7 @@
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>작업 중</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -28657,7 +28657,7 @@
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -28919,7 +28919,7 @@
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>이력완료</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -29095,7 +29095,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>작업 중</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -29138,7 +29138,7 @@
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>WO업체배정</t>
+          <t>금일착수</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -29181,15 +29181,789 @@
       </c>
       <c r="G656" t="inlineStr">
         <is>
+          <t>이력완료</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>row_1655_0</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>W26BK6947</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>[DS-LT3503] DS-LT3503 STM Tracing 연장작업 및 보온 추가 작업</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
           <t>WO업체배정</t>
         </is>
       </c>
-      <c r="H656" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="I656" t="inlineStr"/>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>row_1656_1</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>W26BK6927</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>윤활유 배합 Strainer 부속구 설치작업</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>배합- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>row_1657_2</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>W26BK6861</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>No.1 LBO 10월 Steam Tracing 및 Trap 수리 작업</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>No.3 VDU</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>작업 중</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>row_1658_3</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>W26BK6860</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>[Y-X0911-T1] Y-X0911 -T1 Calibration Pot Leak로 인한 교체 작업</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>CDW공정</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>YMAC 생산관리</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>금일착수</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>row_1659_4</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>W26BK6659</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>F5203 Element 교체 작업</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>No.2 SRP</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>row_1660_5</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>W26BK6658</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Amine Make Up  준비작업</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>No.2 SRP</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>row_1661_6</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>W26BK6557</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>PAS4010 아민 M/U용 N2 Line 개선작업</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>#2 VRDS UTOS</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>row_1662_7</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>W26BK6060</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>[CD-P0852B] CD-P0852B Seal 수리작업을 위한 사전 Blind 작업</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>CDW공정</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>YMAC 생산관리</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>금일착수</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>row_1663_8</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>W26BK6047</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>VRDS OBL 배관 VDU Vacuum Line STM Tracing Leak수리작업(보온/비계작업 포함)</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>row_1664_9</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>W26BK6046</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>[Y-PSV9101] Y-PSV9101 (HOU C/T LP STM PSV) Support 보강 작업</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>HOU Cooling Tower</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>row_1665_10</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>W26BK6020</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>C2101 N2 Bombe 보관함 개선작업</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Unicracker</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>row_1666_11</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>W26BK6015</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>[VD-F1102A] F1102A(LVGO REFLUX) FILTER 청소 작업</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>No.2 VDU</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>MC(작업완료)</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>row_1667_12</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>W26BK6014</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>고압용기 Bomb 부식방지를 위한 거치대 설치 작업</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>No.1 H2 plant</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>HOU생산1팀</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>row_1668_13</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>W26BK5903</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>CO2 공정 C/W SUPPLY, C/W RETURN 배관 하부 코팅 불량으로 도장 작업</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>CO2 Recovery</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>row_1669_14</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>W26BK5811</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>HOU생산3팀 현장 Sport Shim Plate 보강작업 (VRDS/UTOS)</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>#2 VRDS UTOS</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>HOU생산3팀</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>작업 중</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>row_1670_15</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>W26BK5807</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>윤활유 배합조 상부 맨홀 투입망 설치</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>배합- LUBE 공통</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>윤활유생산</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>row_1671_16</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>W26BK5188</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>[DS-E3311B] BLC 열교환기 Hot Bolting 작업</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>VRDS</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>HOU생산2팀</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>이력완료</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>row_1672_17</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>W26BK5067</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>[CD-SC05006] No.2 LBO CD-SC05006 Support 부식으로 교체 작업(그림 첨부)</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>No.2 CDW</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>일상정비</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>기유생산1</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>WO업체배정</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -29404,7 +29404,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="I661" t="inlineStr"/>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -29406,7 +29406,7 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-29,2026-10-30</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -29451,7 +29451,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="I662" t="inlineStr"/>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -29453,7 +29453,7 @@
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-29,2026-10-30</t>
         </is>
       </c>
     </row>

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -2611,7 +2611,11 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -29365,7 +29365,11 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="I660" t="inlineStr"/>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" s="1" t="inlineStr">

--- a/work_db.xlsx
+++ b/work_db.xlsx
@@ -29236,7 +29236,11 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="I657" t="inlineStr"/>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="1" t="inlineStr">
